--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487947_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487947_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. KOYANOUBA DJIRANGAYE</t>
+          <t>A. GUZMAN SALINAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.9162</v>
+        <v>10.828</v>
       </c>
       <c r="E2" t="n">
-        <v>8.159800000000001</v>
+        <v>7.4813</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7563</v>
+        <v>3.3467</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8946</v>
+        <v>9.2738</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2806</v>
+        <v>2.2849</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6141</v>
+        <v>6.9888</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7167</v>
+        <v>8.026</v>
       </c>
       <c r="K2" t="n">
-        <v>3.195</v>
+        <v>2.4011</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4782</v>
+        <v>5.6249</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1779</v>
+        <v>1.2478</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0856</v>
+        <v>-0.1162</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0923</v>
+        <v>1.364</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7751</v>
+        <v>0.5947</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7751</v>
+        <v>2.5769</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5656</v>
+        <v>0.356</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2886</v>
+        <v>0.2305</v>
       </c>
       <c r="U2" t="n">
-        <v>0.277</v>
+        <v>0.1256</v>
       </c>
       <c r="V2" t="n">
-        <v>2.6808</v>
+        <v>0.6036</v>
       </c>
       <c r="W2" t="n">
-        <v>4.1545</v>
+        <v>1.2071</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.4737</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GUZMAN SALINAS</t>
+          <t>E. KOYANOUBA DJIRANGAYE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.3652</v>
+        <v>10.672</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4397</v>
+        <v>7.7753</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9255</v>
+        <v>2.8967</v>
       </c>
       <c r="G3" t="n">
-        <v>9.2738</v>
+        <v>3.8946</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2849</v>
+        <v>3.2806</v>
       </c>
       <c r="I3" t="n">
-        <v>6.9888</v>
+        <v>0.6141</v>
       </c>
       <c r="J3" t="n">
-        <v>8.026</v>
+        <v>2.7167</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4011</v>
+        <v>3.195</v>
       </c>
       <c r="L3" t="n">
-        <v>5.6249</v>
+        <v>-0.4782</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2478</v>
+        <v>1.1779</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1162</v>
+        <v>0.0856</v>
       </c>
       <c r="O3" t="n">
-        <v>1.364</v>
+        <v>1.0923</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5947</v>
+        <v>2.7751</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5769</v>
+        <v>2.7751</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1068</v>
+        <v>1.3215</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8112</v>
+        <v>0.9041</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2956</v>
+        <v>0.4174</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6036</v>
+        <v>2.6808</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2071</v>
+        <v>4.1545</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6036</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>8.6381</v>
+        <v>8.376300000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0253</v>
+        <v>4.5388</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6129</v>
+        <v>3.8375</v>
       </c>
       <c r="G4" t="n">
         <v>3.1419</v>
@@ -766,13 +766,13 @@
         <v>3.568</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4545</v>
+        <v>0.1927</v>
       </c>
       <c r="T4" t="n">
-        <v>0.727</v>
+        <v>0.2406</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2725</v>
+        <v>-0.0479</v>
       </c>
       <c r="V4" t="n">
         <v>1.4737</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>8.294700000000001</v>
+        <v>7.777</v>
       </c>
       <c r="E5" t="n">
-        <v>6.5293</v>
+        <v>6.3485</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7654</v>
+        <v>1.4285</v>
       </c>
       <c r="G5" t="n">
         <v>4.6474</v>
@@ -844,13 +844,13 @@
         <v>2.5769</v>
       </c>
       <c r="S5" t="n">
-        <v>2.132</v>
+        <v>1.6142</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1014</v>
+        <v>0.9206</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0306</v>
+        <v>0.6936</v>
       </c>
       <c r="V5" t="n">
         <v>-0.0704</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.0733</v>
+        <v>4.6822</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.928</v>
+        <v>-0.7014</v>
       </c>
       <c r="F6" t="n">
-        <v>6.0013</v>
+        <v>5.3836</v>
       </c>
       <c r="G6" t="n">
         <v>2.3098</v>
@@ -922,13 +922,13 @@
         <v>3.3698</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2016</v>
+        <v>1.8106</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4223</v>
+        <v>0.649</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7793</v>
+        <v>1.1616</v>
       </c>
       <c r="V6" t="n">
         <v>2.1476</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W. HASSAN</t>
+          <t>P. BALLESTER MANQUE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.085</v>
+        <v>1.7457</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6077</v>
+        <v>1.1249</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4773</v>
+        <v>0.6208</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.744</v>
+        <v>1.4123</v>
       </c>
       <c r="H7" t="n">
-        <v>0.53</v>
+        <v>-0.3765</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.274</v>
+        <v>1.7888</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4313</v>
+        <v>1.2726</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3165</v>
+        <v>0.0271</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7478</v>
+        <v>1.2455</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3126</v>
+        <v>0.1398</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2136</v>
+        <v>-0.4036</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5262</v>
+        <v>0.5433</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5858</v>
+        <v>0.5947</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5858</v>
+        <v>0.5947</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4394</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>1.039</v>
+        <v>-0.1477</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4003</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1962</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. BALLESTER MANQUE</t>
+          <t>W. HASSAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7</v>
+        <v>1.0797</v>
       </c>
       <c r="E8" t="n">
-        <v>1.023</v>
+        <v>-0.1449</v>
       </c>
       <c r="F8" t="n">
-        <v>0.677</v>
+        <v>1.2246</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4123</v>
+        <v>-0.744</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3765</v>
+        <v>0.53</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7888</v>
+        <v>-1.274</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2726</v>
+        <v>-0.4313</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0271</v>
+        <v>0.3165</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2455</v>
+        <v>-0.7478</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1398</v>
+        <v>-0.3126</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4036</v>
+        <v>0.2136</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5433</v>
+        <v>-0.5262</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5947</v>
+        <v>1.5858</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5947</v>
+        <v>1.5858</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1109</v>
+        <v>0.4341</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2496</v>
+        <v>0.2865</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1387</v>
+        <v>0.1476</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1962</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0044</v>
+        <v>0.1817</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1892</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1849</v>
+        <v>0.2691</v>
       </c>
       <c r="G9" t="n">
         <v>-0.07149999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>0.3964</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3293</v>
+        <v>-0.1432</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2496</v>
+        <v>-0.1477</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.0046</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. CUBERO ROJANO</t>
+          <t>S. TORRECILLAS LAJARA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0935</v>
+        <v>-0.1503</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6921</v>
+        <v>-0.4797</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5986</v>
+        <v>0.3295</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2897</v>
+        <v>-0.9982</v>
       </c>
       <c r="H10" t="n">
-        <v>0.596</v>
+        <v>-1.3101</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8857</v>
+        <v>0.3118</v>
       </c>
       <c r="J10" t="n">
-        <v>0.08890000000000001</v>
+        <v>-0.5986</v>
       </c>
       <c r="K10" t="n">
-        <v>0.72</v>
+        <v>-0.6388</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6312</v>
+        <v>0.0402</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3786</v>
+        <v>-0.3996</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1241</v>
+        <v>-0.6713</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2545</v>
+        <v>0.2717</v>
       </c>
       <c r="P10" t="n">
-        <v>1.784</v>
+        <v>0.9911</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.784</v>
+        <v>0.9911</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0437</v>
+        <v>-0.1432</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.444</v>
+        <v>-0.1477</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4003</v>
+        <v>0.0046</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5441</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.337</v>
+        <v>0.2666</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2071</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. TORRECILLAS LAJARA</t>
+          <t>R. CUBERO ROJANO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3364</v>
+        <v>-0.1819</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5816</v>
+        <v>-0.5279</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2452</v>
+        <v>0.3459</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9982</v>
+        <v>-0.2897</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3101</v>
+        <v>0.596</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3118</v>
+        <v>-0.8857</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5986</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6388</v>
+        <v>0.72</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0402</v>
+        <v>-0.6312</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3996</v>
+        <v>-0.3786</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6713</v>
+        <v>-0.1241</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2717</v>
+        <v>-0.2545</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9911</v>
+        <v>1.784</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9911</v>
+        <v>1.784</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3293</v>
+        <v>-0.1321</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2496</v>
+        <v>-0.2798</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.1476</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.5441</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2666</v>
+        <v>-0.337</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2666</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3773</v>
+        <v>-0.293</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5042</v>
+        <v>0.2713</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8731</v>
+        <v>-0.5643</v>
       </c>
       <c r="G12" t="n">
         <v>1.3153</v>
@@ -1390,13 +1390,13 @@
         <v>1.3876</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.545</v>
+        <v>-0.4607</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.1605</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.609</v>
+        <v>-0.3002</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5441</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.9062</v>
+        <v>-2.4269</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.4758</v>
+        <v>-4.2492</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5696</v>
+        <v>1.8223</v>
       </c>
       <c r="G13" t="n">
         <v>-3.1078</v>
@@ -1468,13 +1468,13 @@
         <v>1.1893</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0033</v>
+        <v>0.4827</v>
       </c>
       <c r="T13" t="n">
-        <v>0.18</v>
+        <v>0.4066</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1766</v>
+        <v>0.0761</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>41.35470000000001</v>
+        <v>42.29050000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>20.4139</v>
+        <v>21.3496</v>
       </c>
       <c r="F14" t="n">
         <v>20.9409</v>
@@ -1528,7 +1528,7 @@
         <v>3.1107</v>
       </c>
       <c r="M14" t="n">
-        <v>3.996700000000001</v>
+        <v>3.996699999999999</v>
       </c>
       <c r="N14" t="n">
         <v>-0.1924</v>
@@ -1546,13 +1546,13 @@
         <v>22.7956</v>
       </c>
       <c r="S14" t="n">
-        <v>4.3314</v>
+        <v>5.267399999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8183</v>
+        <v>2.754500000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>2.513100000000001</v>
+        <v>2.5132</v>
       </c>
       <c r="V14" t="n">
         <v>3.3547</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. ESPINAL REYNOSO</t>
+          <t>J. MORALES MUÑOZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6052</v>
+        <v>0.3027</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1128</v>
+        <v>0.3027</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5076</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.1795</v>
+        <v>0.3027</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3524</v>
+        <v>0.3027</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.8272</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4095</v>
+        <v>0.3027</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9086</v>
+        <v>0.3027</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3181</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.77</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2609</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5091</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.3964</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.983</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2975</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6855</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.6213</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MORALES MUÑOZ</t>
+          <t>J. ESPINAL REYNOSO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3027</v>
+        <v>-0.0373</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3027</v>
+        <v>2.8072</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-2.8446</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3027</v>
+        <v>-2.1795</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3027</v>
+        <v>-0.3524</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-1.8272</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3027</v>
+        <v>-0.4095</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3027</v>
+        <v>0.9086</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-1.3181</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-1.77</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-1.2609</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.5091</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.3964</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.3404</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.0081</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.3485</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.6213</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6885</v>
+        <v>-1.8328</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.5298</v>
+        <v>-2.0391</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1587</v>
+        <v>0.2063</v>
       </c>
       <c r="G17" t="n">
         <v>0.3946</v>
@@ -1780,13 +1780,13 @@
         <v>0.5947</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8308</v>
+        <v>0.6865</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7343</v>
+        <v>0.2249</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0965</v>
+        <v>0.4615</v>
       </c>
       <c r="V17" t="n">
         <v>-0.337</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1776</v>
+        <v>-1.9281</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9474</v>
+        <v>-0.6418</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2302</v>
+        <v>-1.2864</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5365</v>
@@ -1858,13 +1858,13 @@
         <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2378</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8001</v>
+        <v>-0.4945</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4377</v>
+        <v>-0.4938</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1962</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. BUSTO VERANO</t>
+          <t>R. URBANO MORENO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4115</v>
+        <v>-2.1596</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1068</v>
+        <v>-0.4123</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3048</v>
+        <v>-1.7473</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.0947</v>
+        <v>0.4347</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1836</v>
+        <v>-2.125</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9112</v>
+        <v>2.5597</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.1165</v>
+        <v>0.2639</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0467</v>
+        <v>-0.3828</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.0698</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9782</v>
+        <v>0.1708</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1369</v>
+        <v>-1.7422</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1586</v>
+        <v>1.913</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7929</v>
+        <v>1.1893</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.1982</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9911</v>
+        <v>1.3876</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3763</v>
+        <v>-0.4993</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0586</v>
+        <v>-0.478</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3177</v>
+        <v>-0.0213</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2666</v>
+        <v>-3.2843</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-3.2843</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. URBANO MORENO</t>
+          <t>D. BUSTO VERANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5285</v>
+        <v>-2.7557</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9216</v>
+        <v>-2.3105</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6069</v>
+        <v>-0.4452</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4347</v>
+        <v>-3.0947</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.125</v>
+        <v>-1.1836</v>
       </c>
       <c r="I20" t="n">
-        <v>2.5597</v>
+        <v>-1.9112</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2639</v>
+        <v>-2.1165</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3828</v>
+        <v>-0.0467</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6467000000000001</v>
+        <v>-2.0698</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1708</v>
+        <v>-0.9782</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7422</v>
+        <v>-1.1369</v>
       </c>
       <c r="O20" t="n">
-        <v>1.913</v>
+        <v>0.1586</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.1982</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3876</v>
+        <v>0.9911</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8682</v>
+        <v>-0.7204</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9873</v>
+        <v>-0.2623</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1191</v>
+        <v>-0.4581</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.2843</v>
+        <v>0.2666</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.2843</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2796</v>
+        <v>-3.2235</v>
       </c>
       <c r="E21" t="n">
         <v>-1.0333</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2463</v>
+        <v>-2.1901</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4015</v>
@@ -2092,13 +2092,13 @@
         <v>0.1982</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2745</v>
+        <v>-0.2184</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1762</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0984</v>
+        <v>-0.0422</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6036</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5756</v>
+        <v>-4.2837</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9253</v>
+        <v>-2.2122</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6503</v>
+        <v>-2.0715</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8406</v>
@@ -2170,13 +2170,13 @@
         <v>1.3876</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6407</v>
+        <v>-0.3488</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3103</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6697</v>
+        <v>0.2485</v>
       </c>
       <c r="V22" t="n">
         <v>2.0772</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.0787</v>
+        <v>-5.1129</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.271</v>
+        <v>-1.5579</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.8077</v>
+        <v>-3.555</v>
       </c>
       <c r="G23" t="n">
         <v>-2.613</v>
@@ -2248,13 +2248,13 @@
         <v>0.7929</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.001</v>
+        <v>-1.0352</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1855</v>
+        <v>-0.4725</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8154</v>
+        <v>-0.5627</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8701</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. MARTINEZ GUZMAN</t>
+          <t>J. REYES ORTEGA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1653</v>
+        <v>-6.4677</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9951</v>
+        <v>-4.7419</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.1701</v>
+        <v>-1.7258</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.1854</v>
+        <v>-3.4685</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.9857</v>
+        <v>-3.411</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1996</v>
+        <v>-0.0576</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.656</v>
+        <v>-1.4889</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.656</v>
+        <v>-2.2121</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.7232</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5294</v>
+        <v>-1.9796</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3298</v>
+        <v>-1.1989</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.1996</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1982</v>
+        <v>-2.1805</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.1982</v>
+        <v>-2.9733</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3964</v>
+        <v>0.7929</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2361</v>
+        <v>-0.4818</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8591</v>
+        <v>0.1277</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.623</v>
+        <v>-0.6095</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.4142</v>
+        <v>-0.337</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.4074</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.4142</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. REYES ORTEGA</t>
+          <t>J. MARTINEZ GUZMAN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.3867</v>
+        <v>-6.896</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.4363</v>
+        <v>-2.8101</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.9505</v>
+        <v>-4.0859</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.4685</v>
+        <v>-4.1854</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.411</v>
+        <v>-2.9857</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0576</v>
+        <v>-1.1996</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.4889</v>
+        <v>-2.656</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.2121</v>
+        <v>-2.656</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7232</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.9796</v>
+        <v>-1.5294</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.1989</v>
+        <v>-0.3298</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.7806999999999999</v>
+        <v>-1.1996</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.1805</v>
+        <v>0.1982</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.9733</v>
+        <v>-0.1982</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7929</v>
+        <v>0.3964</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4008</v>
+        <v>-0.4946</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4333</v>
+        <v>0.0441</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8341</v>
+        <v>-0.5387</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.337</v>
+        <v>-2.4142</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.4074</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0704</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.9706</v>
+        <v>-6.9601</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.1899</v>
+        <v>-6.2917</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.7806999999999999</v>
+        <v>-0.6684</v>
       </c>
       <c r="G26" t="n">
         <v>0.4039</v>
@@ -2482,13 +2482,13 @@
         <v>1.3876</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.5717</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3192</v>
+        <v>-0.4211</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.263</v>
+        <v>-0.1506</v>
       </c>
       <c r="V26" t="n">
         <v>1.1367</v>
@@ -2518,10 +2518,10 @@
         <v>-41.35469999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-20.941</v>
+        <v>-20.9409</v>
       </c>
       <c r="F27" t="n">
-        <v>-20.4138</v>
+        <v>-20.41389999999999</v>
       </c>
       <c r="G27" t="n">
         <v>-20.7838</v>
@@ -2560,13 +2560,13 @@
         <v>9.911200000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>-4.3316</v>
+        <v>-4.3317</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.513</v>
+        <v>-2.513300000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.8185</v>
+        <v>-1.8184</v>
       </c>
       <c r="V27" t="n">
         <v>-3.3548</v>
